--- a/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20760" windowHeight="10800"/>
+    <workbookView windowWidth="28800" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="343">
   <si>
     <t>##column#var</t>
   </si>
@@ -1083,6 +1083,24 @@
   </si>
   <si>
     <t>重置天赋</t>
+  </si>
+  <si>
+    <t>AffinityMax</t>
+  </si>
+  <si>
+    <t>最大亲和值</t>
+  </si>
+  <si>
+    <t>Fun</t>
+  </si>
+  <si>
+    <t>最大趣味值</t>
+  </si>
+  <si>
+    <t>Violence</t>
+  </si>
+  <si>
+    <t>最大暴力值</t>
   </si>
 </sst>
 </file>
@@ -2113,7 +2131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="24.125" style="1" customWidth="1"/>
@@ -4526,6 +4544,48 @@
         <v>139</v>
       </c>
     </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="1">
+        <v>50</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="1">
+        <v>50</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="1">
+        <v>50</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C112" r:id="rId3" display="1000001;100@601800051"/>
